--- a/Sabesp Trade - Nominal Hcs - 11.05.2026.xlsx
+++ b/Sabesp Trade - Nominal Hcs - 11.05.2026.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssricardo\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{914285F9-84F2-418E-87BF-FBE553C3CCC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A008C41-BB56-4780-9128-E2D85FAC68FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Nominal" sheetId="1" r:id="rId1"/>
-    <sheet name="Resumo" sheetId="3" r:id="rId2"/>
+    <sheet name="Nominal Geral" sheetId="1" r:id="rId1"/>
+    <sheet name="Nominal Freguesia e Santana" sheetId="4" r:id="rId2"/>
+    <sheet name="Resumo" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Nominal!$A$1:$Q$349</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nominal Geral'!$A$1:$S$349</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3897" uniqueCount="844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4843" uniqueCount="846">
   <si>
     <t>MATRICULA</t>
   </si>
@@ -2572,6 +2573,12 @@
   </si>
   <si>
     <t>RUA PORTO RICO, JARDIM DEBORA, 116, Poa, 8555660</t>
+  </si>
+  <si>
+    <t>Distância até Casa Verde (km)</t>
+  </si>
+  <si>
+    <t>Tempo Estimado (min)</t>
   </si>
 </sst>
 </file>
@@ -2691,7 +2698,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -2741,12 +2748,40 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3038,7 +3073,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q349"/>
+  <dimension ref="A1:S349"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -3056,9 +3091,11 @@
     <col min="15" max="15" width="27.85546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="65.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="95.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.85546875" style="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3110,8 +3147,14 @@
       <c r="Q1" s="3" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" s="18" t="s">
+        <v>844</v>
+      </c>
+      <c r="S1" s="18" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>376235</v>
       </c>
@@ -3161,8 +3204,14 @@
       <c r="Q2" s="7" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R2" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S2" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>376343</v>
       </c>
@@ -3212,8 +3261,14 @@
       <c r="Q3" s="7" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R3" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S3" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>376254</v>
       </c>
@@ -3263,8 +3318,14 @@
       <c r="Q4" s="7" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R4" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S4" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>376185</v>
       </c>
@@ -3314,8 +3375,14 @@
       <c r="Q5" s="7" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R5" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S5" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>376263</v>
       </c>
@@ -3365,8 +3432,14 @@
       <c r="Q6" s="7" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R6" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S6" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>376264</v>
       </c>
@@ -3416,8 +3489,14 @@
       <c r="Q7" s="7" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R7" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S7" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>376255</v>
       </c>
@@ -3467,8 +3546,14 @@
       <c r="Q8" s="7" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R8" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S8" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>376256</v>
       </c>
@@ -3518,8 +3603,14 @@
       <c r="Q9" s="7" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R9" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S9" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>376560</v>
       </c>
@@ -3569,8 +3660,14 @@
       <c r="Q10" s="7" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R10" s="19">
+        <v>2.99</v>
+      </c>
+      <c r="S10" s="19">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>376310</v>
       </c>
@@ -3620,8 +3717,14 @@
       <c r="Q11" s="7" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R11" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S11" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>376257</v>
       </c>
@@ -3671,8 +3774,14 @@
       <c r="Q12" s="7" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R12" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S12" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>376189</v>
       </c>
@@ -3722,8 +3831,14 @@
       <c r="Q13" s="7" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R13" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S13" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>376287</v>
       </c>
@@ -3775,8 +3890,14 @@
       <c r="Q14" s="7" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R14" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S14" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>376190</v>
       </c>
@@ -3826,8 +3947,14 @@
       <c r="Q15" s="7" t="s">
         <v>510</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R15" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S15" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>376296</v>
       </c>
@@ -3877,8 +4004,14 @@
       <c r="Q16" s="7" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R16" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S16" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>376341</v>
       </c>
@@ -3928,8 +4061,14 @@
       <c r="Q17" s="7" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R17" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S17" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>376297</v>
       </c>
@@ -3979,8 +4118,14 @@
       <c r="Q18" s="7" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R18" s="19">
+        <v>6.83</v>
+      </c>
+      <c r="S18" s="19">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>376157</v>
       </c>
@@ -4030,8 +4175,14 @@
       <c r="Q19" s="7" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R19" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S19" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>376244</v>
       </c>
@@ -4081,8 +4232,14 @@
       <c r="Q20" s="7" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R20" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S20" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>376258</v>
       </c>
@@ -4132,8 +4289,14 @@
       <c r="Q21" s="7" t="s">
         <v>516</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R21" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S21" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>376277</v>
       </c>
@@ -4183,8 +4346,14 @@
       <c r="Q22" s="7" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R22" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S22" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>376553</v>
       </c>
@@ -4234,8 +4403,14 @@
       <c r="Q23" s="7" t="s">
         <v>518</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R23" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S23" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>376230</v>
       </c>
@@ -4285,8 +4460,14 @@
       <c r="Q24" s="7" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R24" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S24" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>376298</v>
       </c>
@@ -4336,8 +4517,14 @@
       <c r="Q25" s="7" t="s">
         <v>520</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R25" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S25" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>376242</v>
       </c>
@@ -4387,8 +4574,14 @@
       <c r="Q26" s="7" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R26" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S26" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>376226</v>
       </c>
@@ -4438,8 +4631,14 @@
       <c r="Q27" s="7" t="s">
         <v>522</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R27" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S27" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>376299</v>
       </c>
@@ -4489,8 +4688,14 @@
       <c r="Q28" s="7" t="s">
         <v>523</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R28" s="19">
+        <v>2.42</v>
+      </c>
+      <c r="S28" s="19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>376439</v>
       </c>
@@ -4540,8 +4745,14 @@
       <c r="Q29" s="7" t="s">
         <v>524</v>
       </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R29" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S29" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>376218</v>
       </c>
@@ -4591,8 +4802,14 @@
       <c r="Q30" s="7" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R30" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S30" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>376192</v>
       </c>
@@ -4642,8 +4859,14 @@
       <c r="Q31" s="7" t="s">
         <v>526</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R31" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S31" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>376401</v>
       </c>
@@ -4693,8 +4916,14 @@
       <c r="Q32" s="7" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R32" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S32" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>376342</v>
       </c>
@@ -4744,8 +4973,14 @@
       <c r="Q33" s="7" t="s">
         <v>528</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R33" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S33" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>376237</v>
       </c>
@@ -4795,8 +5030,14 @@
       <c r="Q34" s="7" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R34" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S34" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>376186</v>
       </c>
@@ -4846,8 +5087,14 @@
       <c r="Q35" s="7" t="s">
         <v>530</v>
       </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R35" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S35" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>376300</v>
       </c>
@@ -4897,8 +5144,14 @@
       <c r="Q36" s="7" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R36" s="19">
+        <v>10.65</v>
+      </c>
+      <c r="S36" s="19">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>376193</v>
       </c>
@@ -4948,8 +5201,14 @@
       <c r="Q37" s="7" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R37" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S37" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>376194</v>
       </c>
@@ -4999,8 +5258,14 @@
       <c r="Q38" s="7" t="s">
         <v>533</v>
       </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R38" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S38" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>376293</v>
       </c>
@@ -5050,8 +5315,14 @@
       <c r="Q39" s="7" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R39" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S39" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>376195</v>
       </c>
@@ -5101,8 +5372,14 @@
       <c r="Q40" s="7" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R40" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S40" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>376196</v>
       </c>
@@ -5152,8 +5429,14 @@
       <c r="Q41" s="7" t="s">
         <v>536</v>
       </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R41" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S41" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>376219</v>
       </c>
@@ -5203,8 +5486,14 @@
       <c r="Q42" s="7" t="s">
         <v>537</v>
       </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R42" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S42" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>376245</v>
       </c>
@@ -5254,8 +5543,14 @@
       <c r="Q43" s="7" t="s">
         <v>538</v>
       </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R43" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S43" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>376301</v>
       </c>
@@ -5305,8 +5600,14 @@
       <c r="Q44" s="7" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R44" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S44" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>376228</v>
       </c>
@@ -5356,8 +5657,14 @@
       <c r="Q45" s="7" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R45" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S45" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>376399</v>
       </c>
@@ -5407,8 +5714,14 @@
       <c r="Q46" s="7" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R46" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S46" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>376308</v>
       </c>
@@ -5458,8 +5771,14 @@
       <c r="Q47" s="7" t="s">
         <v>542</v>
       </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R47" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S47" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>376355</v>
       </c>
@@ -5509,8 +5828,14 @@
       <c r="Q48" s="7" t="s">
         <v>543</v>
       </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R48" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S48" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>376402</v>
       </c>
@@ -5560,8 +5885,14 @@
       <c r="Q49" s="7" t="s">
         <v>544</v>
       </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R49" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S49" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>376312</v>
       </c>
@@ -5611,8 +5942,14 @@
       <c r="Q50" s="7" t="s">
         <v>545</v>
       </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R50" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S50" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>376250</v>
       </c>
@@ -5662,8 +5999,14 @@
       <c r="Q51" s="7" t="s">
         <v>546</v>
       </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R51" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S51" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>376292</v>
       </c>
@@ -5713,8 +6056,14 @@
       <c r="Q52" s="7" t="s">
         <v>547</v>
       </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R52" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S52" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>376197</v>
       </c>
@@ -5764,8 +6113,14 @@
       <c r="Q53" s="7" t="s">
         <v>548</v>
       </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R53" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S53" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>376280</v>
       </c>
@@ -5815,8 +6170,14 @@
       <c r="Q54" s="7" t="s">
         <v>549</v>
       </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R54" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S54" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>376291</v>
       </c>
@@ -5866,8 +6227,14 @@
       <c r="Q55" s="7" t="s">
         <v>550</v>
       </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R55" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S55" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>376198</v>
       </c>
@@ -5917,8 +6284,14 @@
       <c r="Q56" s="7" t="s">
         <v>551</v>
       </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R56" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S56" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>376253</v>
       </c>
@@ -5968,8 +6341,14 @@
       <c r="Q57" s="7" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R57" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S57" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>376552</v>
       </c>
@@ -6019,8 +6398,14 @@
       <c r="Q58" s="7" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R58" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S58" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>376302</v>
       </c>
@@ -6070,8 +6455,14 @@
       <c r="Q59" s="7" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R59" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S59" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>376303</v>
       </c>
@@ -6121,8 +6512,14 @@
       <c r="Q60" s="7" t="s">
         <v>555</v>
       </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R60" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S60" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>376175</v>
       </c>
@@ -6172,8 +6569,14 @@
       <c r="Q61" s="7" t="s">
         <v>556</v>
       </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R61" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S61" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>376304</v>
       </c>
@@ -6223,8 +6626,14 @@
       <c r="Q62" s="7" t="s">
         <v>557</v>
       </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R62" s="19">
+        <v>9.2100000000000009</v>
+      </c>
+      <c r="S62" s="19">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>376243</v>
       </c>
@@ -6276,8 +6685,14 @@
       <c r="Q63" s="7" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R63" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S63" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>376199</v>
       </c>
@@ -6327,8 +6742,14 @@
       <c r="Q64" s="7" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R64" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S64" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>376290</v>
       </c>
@@ -6378,8 +6799,14 @@
       <c r="Q65" s="7" t="s">
         <v>560</v>
       </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R65" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S65" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>376314</v>
       </c>
@@ -6429,8 +6856,14 @@
       <c r="Q66" s="7" t="s">
         <v>561</v>
       </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R66" s="19">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="S66" s="19">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>376305</v>
       </c>
@@ -6480,8 +6913,14 @@
       <c r="Q67" s="7" t="s">
         <v>562</v>
       </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R67" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S67" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>376306</v>
       </c>
@@ -6531,8 +6970,14 @@
       <c r="Q68" s="7" t="s">
         <v>563</v>
       </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R68" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S68" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>376307</v>
       </c>
@@ -6582,8 +7027,14 @@
       <c r="Q69" s="7" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R69" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S69" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>376281</v>
       </c>
@@ -6633,8 +7084,14 @@
       <c r="Q70" s="7" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R70" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S70" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>376234</v>
       </c>
@@ -6684,8 +7141,14 @@
       <c r="Q71" s="7" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R71" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S71" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>376200</v>
       </c>
@@ -6735,8 +7198,14 @@
       <c r="Q72" s="7" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R72" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S72" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>376201</v>
       </c>
@@ -6786,8 +7255,14 @@
       <c r="Q73" s="7" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R73" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S73" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>376288</v>
       </c>
@@ -6837,8 +7312,14 @@
       <c r="Q74" s="7" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R74" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S74" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>376265</v>
       </c>
@@ -6888,8 +7369,14 @@
       <c r="Q75" s="7" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R75" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S75" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
         <v>376220</v>
       </c>
@@ -6939,8 +7426,14 @@
       <c r="Q76" s="7" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R76" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S76" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>376390</v>
       </c>
@@ -6990,8 +7483,14 @@
       <c r="Q77" s="7" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R77" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S77" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>376357</v>
       </c>
@@ -7041,8 +7540,14 @@
       <c r="Q78" s="7" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R78" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S78" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>376364</v>
       </c>
@@ -7092,8 +7597,14 @@
       <c r="Q79" s="7" t="s">
         <v>574</v>
       </c>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R79" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S79" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
         <v>376393</v>
       </c>
@@ -7143,8 +7654,14 @@
       <c r="Q80" s="7" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R80" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S80" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>376366</v>
       </c>
@@ -7194,8 +7711,14 @@
       <c r="Q81" s="7" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R81" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S81" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
         <v>376363</v>
       </c>
@@ -7247,8 +7770,14 @@
       <c r="Q82" s="7" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R82" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S82" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>376202</v>
       </c>
@@ -7298,8 +7827,14 @@
       <c r="Q83" s="7" t="s">
         <v>578</v>
       </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R83" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S83" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
         <v>376282</v>
       </c>
@@ -7349,8 +7884,14 @@
       <c r="Q84" s="7" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R84" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S84" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
         <v>376184</v>
       </c>
@@ -7400,8 +7941,14 @@
       <c r="Q85" s="7" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R85" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S85" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
         <v>376203</v>
       </c>
@@ -7451,8 +7998,14 @@
       <c r="Q86" s="7" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R86" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S86" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
         <v>376279</v>
       </c>
@@ -7502,8 +8055,14 @@
       <c r="Q87" s="7" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R87" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S87" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
         <v>376239</v>
       </c>
@@ -7553,8 +8112,14 @@
       <c r="Q88" s="7" t="s">
         <v>583</v>
       </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R88" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S88" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
         <v>376278</v>
       </c>
@@ -7604,8 +8169,14 @@
       <c r="Q89" s="7" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R89" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S89" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
         <v>376222</v>
       </c>
@@ -7655,8 +8226,14 @@
       <c r="Q90" s="7" t="s">
         <v>585</v>
       </c>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R90" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S90" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
         <v>376248</v>
       </c>
@@ -7706,8 +8283,14 @@
       <c r="Q91" s="7" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R91" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S91" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
         <v>376367</v>
       </c>
@@ -7757,8 +8340,14 @@
       <c r="Q92" s="7" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R92" s="19">
+        <v>6.79</v>
+      </c>
+      <c r="S92" s="19">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
         <v>376391</v>
       </c>
@@ -7808,8 +8397,14 @@
       <c r="Q93" s="7" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R93" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S93" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
         <v>376368</v>
       </c>
@@ -7861,8 +8456,14 @@
       <c r="Q94" s="7" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R94" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S94" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
         <v>376171</v>
       </c>
@@ -7912,8 +8513,14 @@
       <c r="Q95" s="7" t="s">
         <v>590</v>
       </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R95" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S95" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
         <v>376369</v>
       </c>
@@ -7963,8 +8570,14 @@
       <c r="Q96" s="7" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R96" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S96" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
         <v>376350</v>
       </c>
@@ -8014,8 +8627,14 @@
       <c r="Q97" s="7" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R97" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S97" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
         <v>376346</v>
       </c>
@@ -8065,8 +8684,14 @@
       <c r="Q98" s="7" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R98" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S98" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
         <v>376370</v>
       </c>
@@ -8116,8 +8741,14 @@
       <c r="Q99" s="7" t="s">
         <v>594</v>
       </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R99" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S99" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
         <v>376284</v>
       </c>
@@ -8167,8 +8798,14 @@
       <c r="Q100" s="7" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R100" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S100" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
         <v>376365</v>
       </c>
@@ -8218,8 +8855,14 @@
       <c r="Q101" s="7" t="s">
         <v>596</v>
       </c>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R101" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S101" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102" s="4">
         <v>376205</v>
       </c>
@@ -8269,8 +8912,14 @@
       <c r="Q102" s="7" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R102" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S102" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
         <v>376232</v>
       </c>
@@ -8320,8 +8969,14 @@
       <c r="Q103" s="7" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R103" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S103" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A104" s="4">
         <v>376271</v>
       </c>
@@ -8371,8 +9026,14 @@
       <c r="Q104" s="7" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R104" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S104" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A105" s="4">
         <v>376371</v>
       </c>
@@ -8422,8 +9083,14 @@
       <c r="Q105" s="7" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R105" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S105" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A106" s="4">
         <v>376394</v>
       </c>
@@ -8473,8 +9140,14 @@
       <c r="Q106" s="7" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R106" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S106" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
         <v>376386</v>
       </c>
@@ -8524,8 +9197,14 @@
       <c r="Q107" s="7" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R107" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S107" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A108" s="4">
         <v>376398</v>
       </c>
@@ -8575,8 +9254,14 @@
       <c r="Q108" s="7" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R108" s="19">
+        <v>13.34</v>
+      </c>
+      <c r="S108" s="19">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
         <v>376238</v>
       </c>
@@ -8626,8 +9311,14 @@
       <c r="Q109" s="7" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R109" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S109" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
         <v>376372</v>
       </c>
@@ -8677,8 +9368,14 @@
       <c r="Q110" s="7" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R110" s="19">
+        <v>2.7</v>
+      </c>
+      <c r="S110" s="19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
         <v>376206</v>
       </c>
@@ -8728,8 +9425,14 @@
       <c r="Q111" s="7" t="s">
         <v>606</v>
       </c>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R111" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S111" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
         <v>376207</v>
       </c>
@@ -8779,8 +9482,14 @@
       <c r="Q112" s="7" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R112" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S112" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A113" s="4">
         <v>376373</v>
       </c>
@@ -8830,8 +9539,14 @@
       <c r="Q113" s="7" t="s">
         <v>608</v>
       </c>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R113" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S113" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A114" s="4">
         <v>376387</v>
       </c>
@@ -8881,8 +9596,14 @@
       <c r="Q114" s="7" t="s">
         <v>609</v>
       </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R114" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S114" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
         <v>376269</v>
       </c>
@@ -8932,8 +9653,14 @@
       <c r="Q115" s="7" t="s">
         <v>610</v>
       </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R115" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S115" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A116" s="4">
         <v>376361</v>
       </c>
@@ -8983,8 +9710,14 @@
       <c r="Q116" s="7" t="s">
         <v>611</v>
       </c>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R116" s="19">
+        <v>10.1</v>
+      </c>
+      <c r="S116" s="19">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
         <v>376270</v>
       </c>
@@ -9034,8 +9767,14 @@
       <c r="Q117" s="7" t="s">
         <v>612</v>
       </c>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R117" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S117" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A118" s="4">
         <v>376231</v>
       </c>
@@ -9085,8 +9824,14 @@
       <c r="Q118" s="7" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R118" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S118" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
         <v>376374</v>
       </c>
@@ -9136,8 +9881,14 @@
       <c r="Q119" s="7" t="s">
         <v>614</v>
       </c>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R119" s="19">
+        <v>4.58</v>
+      </c>
+      <c r="S119" s="19">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A120" s="4">
         <v>376437</v>
       </c>
@@ -9187,8 +9938,14 @@
       <c r="Q120" s="7" t="s">
         <v>615</v>
       </c>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R120" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S120" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
         <v>376209</v>
       </c>
@@ -9238,8 +9995,14 @@
       <c r="Q121" s="7" t="s">
         <v>616</v>
       </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R121" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S121" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A122" s="4">
         <v>376247</v>
       </c>
@@ -9289,8 +10052,14 @@
       <c r="Q122" s="7" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R122" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S122" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
         <v>376267</v>
       </c>
@@ -9340,8 +10109,14 @@
       <c r="Q123" s="7" t="s">
         <v>618</v>
       </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R123" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S123" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A124" s="4">
         <v>376210</v>
       </c>
@@ -9391,8 +10166,14 @@
       <c r="Q124" s="7" t="s">
         <v>619</v>
       </c>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R124" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S124" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
         <v>376389</v>
       </c>
@@ -9442,8 +10223,14 @@
       <c r="Q125" s="7" t="s">
         <v>620</v>
       </c>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R125" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S125" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A126" s="4">
         <v>376358</v>
       </c>
@@ -9493,8 +10280,14 @@
       <c r="Q126" s="7" t="s">
         <v>621</v>
       </c>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R126" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S126" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A127" s="4">
         <v>376211</v>
       </c>
@@ -9544,8 +10337,14 @@
       <c r="Q127" s="7" t="s">
         <v>622</v>
       </c>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R127" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S127" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A128" s="4">
         <v>376259</v>
       </c>
@@ -9595,8 +10394,14 @@
       <c r="Q128" s="7" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R128" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S128" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="129" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A129" s="4">
         <v>375878</v>
       </c>
@@ -9646,8 +10451,14 @@
       <c r="Q129" s="7" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R129" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S129" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="130" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A130" s="4">
         <v>376188</v>
       </c>
@@ -9697,8 +10508,14 @@
       <c r="Q130" s="7" t="s">
         <v>625</v>
       </c>
-    </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R130" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S130" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="131" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A131" s="4">
         <v>376212</v>
       </c>
@@ -9748,8 +10565,14 @@
       <c r="Q131" s="7" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R131" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S131" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="132" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A132" s="4">
         <v>376353</v>
       </c>
@@ -9799,8 +10622,14 @@
       <c r="Q132" s="7" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R132" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S132" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="133" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A133" s="4">
         <v>376285</v>
       </c>
@@ -9850,8 +10679,14 @@
       <c r="Q133" s="7" t="s">
         <v>628</v>
       </c>
-    </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R133" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S133" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="134" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A134" s="4">
         <v>376159</v>
       </c>
@@ -9901,8 +10736,14 @@
       <c r="Q134" s="7" t="s">
         <v>629</v>
       </c>
-    </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R134" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S134" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="135" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
         <v>376102</v>
       </c>
@@ -9952,8 +10793,14 @@
       <c r="Q135" s="7" t="s">
         <v>630</v>
       </c>
-    </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R135" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S135" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="136" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A136" s="4">
         <v>376345</v>
       </c>
@@ -10003,8 +10850,14 @@
       <c r="Q136" s="7" t="s">
         <v>631</v>
       </c>
-    </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R136" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S136" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="137" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A137" s="4">
         <v>376351</v>
       </c>
@@ -10054,8 +10907,14 @@
       <c r="Q137" s="7" t="s">
         <v>632</v>
       </c>
-    </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R137" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S137" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="138" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A138" s="4">
         <v>376229</v>
       </c>
@@ -10105,8 +10964,14 @@
       <c r="Q138" s="7" t="s">
         <v>633</v>
       </c>
-    </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R138" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S138" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="139" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A139" s="4">
         <v>376375</v>
       </c>
@@ -10156,8 +11021,14 @@
       <c r="Q139" s="7" t="s">
         <v>634</v>
       </c>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R139" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S139" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="140" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A140" s="4">
         <v>376347</v>
       </c>
@@ -10207,8 +11078,14 @@
       <c r="Q140" s="7" t="s">
         <v>635</v>
       </c>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R140" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S140" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="141" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A141" s="4">
         <v>376274</v>
       </c>
@@ -10258,8 +11135,14 @@
       <c r="Q141" s="7" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R141" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S141" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="142" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A142" s="4">
         <v>376376</v>
       </c>
@@ -10309,8 +11192,14 @@
       <c r="Q142" s="7" t="s">
         <v>637</v>
       </c>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R142" s="19">
+        <v>18.68</v>
+      </c>
+      <c r="S142" s="19">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="143" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A143" s="4">
         <v>376252</v>
       </c>
@@ -10360,8 +11249,14 @@
       <c r="Q143" s="7" t="s">
         <v>638</v>
       </c>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R143" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S143" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="144" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A144" s="4">
         <v>376177</v>
       </c>
@@ -10411,8 +11306,14 @@
       <c r="Q144" s="7" t="s">
         <v>639</v>
       </c>
-    </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R144" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S144" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="145" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A145" s="4">
         <v>376403</v>
       </c>
@@ -10462,8 +11363,14 @@
       <c r="Q145" s="7" t="s">
         <v>640</v>
       </c>
-    </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R145" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S145" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="146" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A146" s="4">
         <v>376260</v>
       </c>
@@ -10513,8 +11420,14 @@
       <c r="Q146" s="7" t="s">
         <v>641</v>
       </c>
-    </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R146" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S146" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="147" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A147" s="4">
         <v>376249</v>
       </c>
@@ -10564,8 +11477,14 @@
       <c r="Q147" s="7" t="s">
         <v>642</v>
       </c>
-    </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R147" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S147" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="148" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A148" s="4">
         <v>376273</v>
       </c>
@@ -10615,8 +11534,14 @@
       <c r="Q148" s="7" t="s">
         <v>643</v>
       </c>
-    </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R148" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S148" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="149" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A149" s="4">
         <v>376214</v>
       </c>
@@ -10666,8 +11591,14 @@
       <c r="Q149" s="7" t="s">
         <v>644</v>
       </c>
-    </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R149" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S149" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="150" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A150" s="4">
         <v>376349</v>
       </c>
@@ -10717,8 +11648,14 @@
       <c r="Q150" s="7" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R150" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S150" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="151" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A151" s="4">
         <v>376377</v>
       </c>
@@ -10768,8 +11705,14 @@
       <c r="Q151" s="7" t="s">
         <v>646</v>
       </c>
-    </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R151" s="19">
+        <v>3.6</v>
+      </c>
+      <c r="S151" s="19">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="152" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A152" s="4">
         <v>376275</v>
       </c>
@@ -10819,8 +11762,14 @@
       <c r="Q152" s="7" t="s">
         <v>647</v>
       </c>
-    </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R152" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S152" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="153" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A153" s="4">
         <v>376379</v>
       </c>
@@ -10870,8 +11819,14 @@
       <c r="Q153" s="7" t="s">
         <v>648</v>
       </c>
-    </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R153" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S153" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="154" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A154" s="4">
         <v>376215</v>
       </c>
@@ -10921,8 +11876,14 @@
       <c r="Q154" s="7" t="s">
         <v>649</v>
       </c>
-    </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R154" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S154" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="155" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A155" s="4">
         <v>376261</v>
       </c>
@@ -10972,8 +11933,14 @@
       <c r="Q155" s="7" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R155" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S155" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="156" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A156" s="4">
         <v>376400</v>
       </c>
@@ -11023,8 +11990,14 @@
       <c r="Q156" s="7" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R156" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S156" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="157" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A157" s="4">
         <v>376180</v>
       </c>
@@ -11074,8 +12047,14 @@
       <c r="Q157" s="7" t="s">
         <v>652</v>
       </c>
-    </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R157" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S157" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="158" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A158" s="4">
         <v>376380</v>
       </c>
@@ -11125,8 +12104,14 @@
       <c r="Q158" s="7" t="s">
         <v>653</v>
       </c>
-    </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R158" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S158" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="159" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A159" s="4">
         <v>376354</v>
       </c>
@@ -11176,8 +12161,14 @@
       <c r="Q159" s="7" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R159" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S159" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="160" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A160" s="4">
         <v>376266</v>
       </c>
@@ -11227,8 +12218,14 @@
       <c r="Q160" s="7" t="s">
         <v>655</v>
       </c>
-    </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R160" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S160" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="161" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A161" s="4">
         <v>376381</v>
       </c>
@@ -11278,8 +12275,14 @@
       <c r="Q161" s="7" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R161" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S161" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="162" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A162" s="4">
         <v>376397</v>
       </c>
@@ -11329,8 +12332,14 @@
       <c r="Q162" s="7" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R162" s="19">
+        <v>24</v>
+      </c>
+      <c r="S162" s="19">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="163" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A163" s="4">
         <v>376216</v>
       </c>
@@ -11380,8 +12389,14 @@
       <c r="Q163" s="7" t="s">
         <v>658</v>
       </c>
-    </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R163" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S163" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="164" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A164" s="4">
         <v>376276</v>
       </c>
@@ -11431,8 +12446,14 @@
       <c r="Q164" s="7" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R164" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S164" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="165" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A165" s="4">
         <v>376225</v>
       </c>
@@ -11482,8 +12503,14 @@
       <c r="Q165" s="7" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R165" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S165" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="166" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A166" s="4">
         <v>376227</v>
       </c>
@@ -11533,8 +12560,14 @@
       <c r="Q166" s="7" t="s">
         <v>661</v>
       </c>
-    </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R166" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S166" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="167" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A167" s="4">
         <v>376383</v>
       </c>
@@ -11584,8 +12617,14 @@
       <c r="Q167" s="7" t="s">
         <v>662</v>
       </c>
-    </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R167" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S167" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="168" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A168" s="4">
         <v>376283</v>
       </c>
@@ -11635,8 +12674,14 @@
       <c r="Q168" s="7" t="s">
         <v>663</v>
       </c>
-    </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R168" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S168" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="169" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A169" s="4">
         <v>376240</v>
       </c>
@@ -11686,8 +12731,14 @@
       <c r="Q169" s="7" t="s">
         <v>664</v>
       </c>
-    </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R169" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S169" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="170" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A170" s="4">
         <v>376392</v>
       </c>
@@ -11739,8 +12790,14 @@
       <c r="Q170" s="7" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R170" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S170" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="171" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A171" s="4">
         <v>376388</v>
       </c>
@@ -11790,8 +12847,14 @@
       <c r="Q171" s="7" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R171" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S171" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="172" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A172" s="4">
         <v>376384</v>
       </c>
@@ -11841,8 +12904,14 @@
       <c r="Q172" s="7" t="s">
         <v>667</v>
       </c>
-    </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R172" s="19">
+        <v>2.87</v>
+      </c>
+      <c r="S172" s="19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="173" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A173" s="4">
         <v>376438</v>
       </c>
@@ -11892,8 +12961,14 @@
       <c r="Q173" s="7" t="s">
         <v>668</v>
       </c>
-    </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R173" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S173" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="174" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A174" s="4">
         <v>376217</v>
       </c>
@@ -11945,8 +13020,14 @@
       <c r="Q174" s="7" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R174" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S174" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="175" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A175" s="4">
         <v>371441</v>
       </c>
@@ -11996,8 +13077,14 @@
       <c r="Q175" s="7" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R175" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S175" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="176" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A176" s="4">
         <v>370710</v>
       </c>
@@ -12047,8 +13134,14 @@
       <c r="Q176" s="7" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R176" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S176" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="177" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A177" s="4">
         <v>370574</v>
       </c>
@@ -12098,8 +13191,14 @@
       <c r="Q177" s="7" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R177" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S177" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="178" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A178" s="4">
         <v>370734</v>
       </c>
@@ -12149,8 +13248,14 @@
       <c r="Q178" s="7" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R178" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S178" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="179" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A179" s="4">
         <v>370760</v>
       </c>
@@ -12200,8 +13305,14 @@
       <c r="Q179" s="7" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R179" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S179" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="180" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A180" s="4">
         <v>370584</v>
       </c>
@@ -12251,8 +13362,14 @@
       <c r="Q180" s="7" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R180" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S180" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="181" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A181" s="4">
         <v>370793</v>
       </c>
@@ -12302,8 +13419,14 @@
       <c r="Q181" s="7" t="s">
         <v>676</v>
       </c>
-    </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R181" s="19">
+        <v>1.91</v>
+      </c>
+      <c r="S181" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A182" s="4">
         <v>370303</v>
       </c>
@@ -12353,8 +13476,14 @@
       <c r="Q182" s="7" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R182" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S182" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="183" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A183" s="4">
         <v>370609</v>
       </c>
@@ -12404,8 +13533,14 @@
       <c r="Q183" s="7" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R183" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S183" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="184" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A184" s="4">
         <v>370786</v>
       </c>
@@ -12455,8 +13590,14 @@
       <c r="Q184" s="7" t="s">
         <v>679</v>
       </c>
-    </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R184" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S184" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="185" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A185" s="4">
         <v>371419</v>
       </c>
@@ -12506,8 +13647,14 @@
       <c r="Q185" s="7" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R185" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S185" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="186" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A186" s="4">
         <v>370694</v>
       </c>
@@ -12557,8 +13704,14 @@
       <c r="Q186" s="7" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R186" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S186" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="187" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A187" s="4">
         <v>370709</v>
       </c>
@@ -12608,8 +13761,14 @@
       <c r="Q187" s="7" t="s">
         <v>682</v>
       </c>
-    </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R187" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S187" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="188" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A188" s="4">
         <v>370692</v>
       </c>
@@ -12659,8 +13818,14 @@
       <c r="Q188" s="7" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R188" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S188" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="189" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A189" s="4">
         <v>370701</v>
       </c>
@@ -12710,8 +13875,14 @@
       <c r="Q189" s="7" t="s">
         <v>684</v>
       </c>
-    </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R189" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S189" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="190" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A190" s="4">
         <v>370830</v>
       </c>
@@ -12761,8 +13932,14 @@
       <c r="Q190" s="7" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R190" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S190" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="191" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A191" s="4">
         <v>370846</v>
       </c>
@@ -12812,8 +13989,14 @@
       <c r="Q191" s="7" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R191" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S191" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A192" s="4">
         <v>370736</v>
       </c>
@@ -12863,8 +14046,14 @@
       <c r="Q192" s="7" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R192" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S192" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="193" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A193" s="4">
         <v>370852</v>
       </c>
@@ -12914,8 +14103,14 @@
       <c r="Q193" s="7" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R193" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S193" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="194" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A194" s="4">
         <v>370404</v>
       </c>
@@ -12965,8 +14160,14 @@
       <c r="Q194" s="7" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R194" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S194" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="195" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A195" s="4">
         <v>370269</v>
       </c>
@@ -13016,8 +14217,14 @@
       <c r="Q195" s="7" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R195" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S195" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="196" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A196" s="4">
         <v>370575</v>
       </c>
@@ -13067,8 +14274,14 @@
       <c r="Q196" s="7" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R196" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S196" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="197" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A197" s="4">
         <v>370675</v>
       </c>
@@ -13118,8 +14331,14 @@
       <c r="Q197" s="7" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R197" s="19">
+        <v>33.93</v>
+      </c>
+      <c r="S197" s="19">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="198" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A198" s="4">
         <v>370292</v>
       </c>
@@ -13169,8 +14388,14 @@
       <c r="Q198" s="7" t="s">
         <v>693</v>
       </c>
-    </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R198" s="19">
+        <v>38.450000000000003</v>
+      </c>
+      <c r="S198" s="19">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="199" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A199" s="4">
         <v>370738</v>
       </c>
@@ -13220,8 +14445,14 @@
       <c r="Q199" s="7" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R199" s="19">
+        <v>33.17</v>
+      </c>
+      <c r="S199" s="19">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="200" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A200" s="4">
         <v>370753</v>
       </c>
@@ -13271,8 +14502,14 @@
       <c r="Q200" s="7" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R200" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S200" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="201" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A201" s="4">
         <v>370773</v>
       </c>
@@ -13322,8 +14559,14 @@
       <c r="Q201" s="7" t="s">
         <v>696</v>
       </c>
-    </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R201" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S201" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="202" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A202" s="4">
         <v>370790</v>
       </c>
@@ -13373,8 +14616,14 @@
       <c r="Q202" s="7" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R202" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S202" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="203" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A203" s="4">
         <v>370735</v>
       </c>
@@ -13424,8 +14673,14 @@
       <c r="Q203" s="7" t="s">
         <v>698</v>
       </c>
-    </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R203" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S203" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="204" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A204" s="4">
         <v>370713</v>
       </c>
@@ -13475,8 +14730,14 @@
       <c r="Q204" s="7" t="s">
         <v>699</v>
       </c>
-    </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R204" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S204" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="205" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A205" s="4">
         <v>370814</v>
       </c>
@@ -13526,8 +14787,14 @@
       <c r="Q205" s="7" t="s">
         <v>700</v>
       </c>
-    </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R205" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S205" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="206" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A206" s="4">
         <v>370699</v>
       </c>
@@ -13577,8 +14844,14 @@
       <c r="Q206" s="7" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R206" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S206" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="207" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A207" s="4">
         <v>370643</v>
       </c>
@@ -13628,8 +14901,14 @@
       <c r="Q207" s="7" t="s">
         <v>702</v>
       </c>
-    </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R207" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S207" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="208" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A208" s="4">
         <v>371445</v>
       </c>
@@ -13679,8 +14958,14 @@
       <c r="Q208" s="7" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R208" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S208" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="209" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A209" s="4">
         <v>370653</v>
       </c>
@@ -13730,8 +15015,14 @@
       <c r="Q209" s="7" t="s">
         <v>704</v>
       </c>
-    </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R209" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S209" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="210" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A210" s="4">
         <v>370676</v>
       </c>
@@ -13781,8 +15072,14 @@
       <c r="Q210" s="7" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R210" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S210" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="211" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A211" s="4">
         <v>371433</v>
       </c>
@@ -13832,8 +15129,14 @@
       <c r="Q211" s="7" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R211" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S211" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="212" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A212" s="4">
         <v>370707</v>
       </c>
@@ -13883,8 +15186,14 @@
       <c r="Q212" s="7" t="s">
         <v>707</v>
       </c>
-    </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R212" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S212" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="213" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A213" s="4">
         <v>370661</v>
       </c>
@@ -13934,8 +15243,14 @@
       <c r="Q213" s="7" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R213" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S213" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="214" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A214" s="4">
         <v>370774</v>
       </c>
@@ -13985,8 +15300,14 @@
       <c r="Q214" s="7" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R214" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S214" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="215" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A215" s="4">
         <v>370797</v>
       </c>
@@ -14036,8 +15357,14 @@
       <c r="Q215" s="7" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R215" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S215" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="216" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A216" s="4">
         <v>376948</v>
       </c>
@@ -14087,8 +15414,14 @@
       <c r="Q216" s="7" t="s">
         <v>711</v>
       </c>
-    </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R216" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S216" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="217" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A217" s="4">
         <v>376937</v>
       </c>
@@ -14138,8 +15471,14 @@
       <c r="Q217" s="7" t="s">
         <v>712</v>
       </c>
-    </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R217" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S217" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="218" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A218" s="4">
         <v>376944</v>
       </c>
@@ -14189,8 +15528,14 @@
       <c r="Q218" s="7" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R218" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S218" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="219" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A219" s="4">
         <v>376767</v>
       </c>
@@ -14240,8 +15585,14 @@
       <c r="Q219" s="7" t="s">
         <v>714</v>
       </c>
-    </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R219" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S219" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="220" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A220" s="4">
         <v>376952</v>
       </c>
@@ -14291,8 +15642,14 @@
       <c r="Q220" s="7" t="s">
         <v>715</v>
       </c>
-    </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R220" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S220" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="221" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A221" s="4">
         <v>376766</v>
       </c>
@@ -14342,8 +15699,14 @@
       <c r="Q221" s="7" t="s">
         <v>716</v>
       </c>
-    </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R221" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S221" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="222" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A222" s="4">
         <v>376880</v>
       </c>
@@ -14393,8 +15756,14 @@
       <c r="Q222" s="7" t="s">
         <v>717</v>
       </c>
-    </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R222" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S222" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="223" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A223" s="4">
         <v>376879</v>
       </c>
@@ -14444,8 +15813,14 @@
       <c r="Q223" s="7" t="s">
         <v>718</v>
       </c>
-    </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R223" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S223" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="224" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A224" s="4">
         <v>376943</v>
       </c>
@@ -14495,8 +15870,14 @@
       <c r="Q224" s="7" t="s">
         <v>719</v>
       </c>
-    </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R224" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S224" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="225" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A225" s="4">
         <v>376898</v>
       </c>
@@ -14546,8 +15927,14 @@
       <c r="Q225" s="7" t="s">
         <v>720</v>
       </c>
-    </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R225" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S225" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="226" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A226" s="4">
         <v>376891</v>
       </c>
@@ -14597,8 +15984,14 @@
       <c r="Q226" s="7" t="s">
         <v>721</v>
       </c>
-    </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R226" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S226" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="227" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A227" s="4">
         <v>376759</v>
       </c>
@@ -14648,8 +16041,14 @@
       <c r="Q227" s="7" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R227" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S227" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="228" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A228" s="4">
         <v>376753</v>
       </c>
@@ -14699,8 +16098,14 @@
       <c r="Q228" s="7" t="s">
         <v>723</v>
       </c>
-    </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R228" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S228" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="229" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A229" s="4">
         <v>376763</v>
       </c>
@@ -14750,8 +16155,14 @@
       <c r="Q229" s="7" t="s">
         <v>724</v>
       </c>
-    </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R229" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S229" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="230" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A230" s="4">
         <v>376874</v>
       </c>
@@ -14801,8 +16212,14 @@
       <c r="Q230" s="7" t="s">
         <v>725</v>
       </c>
-    </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R230" s="19">
+        <v>1.43</v>
+      </c>
+      <c r="S230" s="19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="231" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A231" s="4">
         <v>376780</v>
       </c>
@@ -14852,8 +16269,14 @@
       <c r="Q231" s="7" t="s">
         <v>726</v>
       </c>
-    </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R231" s="19">
+        <v>13.51</v>
+      </c>
+      <c r="S231" s="19">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="232" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A232" s="4">
         <v>376892</v>
       </c>
@@ -14903,8 +16326,14 @@
       <c r="Q232" s="7" t="s">
         <v>727</v>
       </c>
-    </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R232" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S232" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="233" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A233" s="4">
         <v>376923</v>
       </c>
@@ -14954,8 +16383,14 @@
       <c r="Q233" s="7" t="s">
         <v>728</v>
       </c>
-    </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R233" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S233" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="234" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A234" s="4">
         <v>376885</v>
       </c>
@@ -15005,8 +16440,14 @@
       <c r="Q234" s="7" t="s">
         <v>729</v>
       </c>
-    </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R234" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S234" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="235" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A235" s="4">
         <v>376926</v>
       </c>
@@ -15056,8 +16497,14 @@
       <c r="Q235" s="7" t="s">
         <v>730</v>
       </c>
-    </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R235" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S235" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="236" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A236" s="4">
         <v>376867</v>
       </c>
@@ -15107,8 +16554,14 @@
       <c r="Q236" s="7" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R236" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S236" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="237" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A237" s="4">
         <v>376866</v>
       </c>
@@ -15158,8 +16611,14 @@
       <c r="Q237" s="7" t="s">
         <v>732</v>
       </c>
-    </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R237" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S237" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="238" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A238" s="4">
         <v>376881</v>
       </c>
@@ -15209,8 +16668,14 @@
       <c r="Q238" s="7" t="s">
         <v>733</v>
       </c>
-    </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R238" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S238" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="239" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A239" s="4">
         <v>376894</v>
       </c>
@@ -15260,8 +16725,14 @@
       <c r="Q239" s="7" t="s">
         <v>734</v>
       </c>
-    </row>
-    <row r="240" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R239" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S239" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="240" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A240" s="4">
         <v>376932</v>
       </c>
@@ -15311,8 +16782,14 @@
       <c r="Q240" s="7" t="s">
         <v>735</v>
       </c>
-    </row>
-    <row r="241" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R240" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S240" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="241" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A241" s="4">
         <v>376863</v>
       </c>
@@ -15362,8 +16839,14 @@
       <c r="Q241" s="7" t="s">
         <v>736</v>
       </c>
-    </row>
-    <row r="242" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R241" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S241" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="242" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A242" s="4">
         <v>376772</v>
       </c>
@@ -15413,8 +16896,14 @@
       <c r="Q242" s="7" t="s">
         <v>737</v>
       </c>
-    </row>
-    <row r="243" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R242" s="19">
+        <v>1.73</v>
+      </c>
+      <c r="S242" s="19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="243" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A243" s="4">
         <v>376917</v>
       </c>
@@ -15464,8 +16953,14 @@
       <c r="Q243" s="7" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="244" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R243" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S243" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="244" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A244" s="4">
         <v>376945</v>
       </c>
@@ -15515,8 +17010,14 @@
       <c r="Q244" s="7" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="245" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R244" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S244" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="245" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A245" s="4">
         <v>376757</v>
       </c>
@@ -15566,8 +17067,14 @@
       <c r="Q245" s="7" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="246" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R245" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S245" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="246" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A246" s="4">
         <v>376899</v>
       </c>
@@ -15617,8 +17124,14 @@
       <c r="Q246" s="7" t="s">
         <v>741</v>
       </c>
-    </row>
-    <row r="247" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R246" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S246" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="247" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A247" s="4">
         <v>376954</v>
       </c>
@@ -15668,8 +17181,14 @@
       <c r="Q247" s="7" t="s">
         <v>742</v>
       </c>
-    </row>
-    <row r="248" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R247" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S247" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="248" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A248" s="4">
         <v>376782</v>
       </c>
@@ -15719,8 +17238,14 @@
       <c r="Q248" s="7" t="s">
         <v>743</v>
       </c>
-    </row>
-    <row r="249" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R248" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S248" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="249" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A249" s="4">
         <v>376882</v>
       </c>
@@ -15770,8 +17295,14 @@
       <c r="Q249" s="7" t="s">
         <v>744</v>
       </c>
-    </row>
-    <row r="250" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R249" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S249" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="250" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A250" s="4">
         <v>376928</v>
       </c>
@@ -15821,8 +17352,14 @@
       <c r="Q250" s="7" t="s">
         <v>745</v>
       </c>
-    </row>
-    <row r="251" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R250" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S250" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="251" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A251" s="4">
         <v>376995</v>
       </c>
@@ -15872,8 +17409,14 @@
       <c r="Q251" s="7" t="s">
         <v>746</v>
       </c>
-    </row>
-    <row r="252" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R251" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S251" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="252" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A252" s="4">
         <v>376895</v>
       </c>
@@ -15923,8 +17466,14 @@
       <c r="Q252" s="7" t="s">
         <v>747</v>
       </c>
-    </row>
-    <row r="253" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R252" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S252" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="253" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A253" s="4">
         <v>376946</v>
       </c>
@@ -15974,8 +17523,14 @@
       <c r="Q253" s="7" t="s">
         <v>748</v>
       </c>
-    </row>
-    <row r="254" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R253" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S253" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="254" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A254" s="4">
         <v>376877</v>
       </c>
@@ -16025,8 +17580,14 @@
       <c r="Q254" s="7" t="s">
         <v>749</v>
       </c>
-    </row>
-    <row r="255" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R254" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S254" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="255" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A255" s="4">
         <v>376768</v>
       </c>
@@ -16076,8 +17637,14 @@
       <c r="Q255" s="7" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="256" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R255" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S255" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="256" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A256" s="4">
         <v>376751</v>
       </c>
@@ -16127,8 +17694,14 @@
       <c r="Q256" s="7" t="s">
         <v>751</v>
       </c>
-    </row>
-    <row r="257" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R256" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S256" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="257" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A257" s="4">
         <v>376756</v>
       </c>
@@ -16178,8 +17751,14 @@
       <c r="Q257" s="7" t="s">
         <v>752</v>
       </c>
-    </row>
-    <row r="258" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R257" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S257" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="258" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A258" s="4">
         <v>376953</v>
       </c>
@@ -16229,8 +17808,14 @@
       <c r="Q258" s="7" t="s">
         <v>753</v>
       </c>
-    </row>
-    <row r="259" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R258" s="19">
+        <v>23.97</v>
+      </c>
+      <c r="S258" s="19">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="259" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A259" s="4">
         <v>376871</v>
       </c>
@@ -16280,8 +17865,14 @@
       <c r="Q259" s="7" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="260" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R259" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S259" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="260" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A260" s="4">
         <v>376781</v>
       </c>
@@ -16331,8 +17922,14 @@
       <c r="Q260" s="7" t="s">
         <v>755</v>
       </c>
-    </row>
-    <row r="261" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R260" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S260" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="261" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A261" s="4">
         <v>376758</v>
       </c>
@@ -16382,8 +17979,14 @@
       <c r="Q261" s="7" t="s">
         <v>756</v>
       </c>
-    </row>
-    <row r="262" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R261" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S261" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="262" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A262" s="4">
         <v>376878</v>
       </c>
@@ -16433,8 +18036,14 @@
       <c r="Q262" s="7" t="s">
         <v>757</v>
       </c>
-    </row>
-    <row r="263" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R262" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S262" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="263" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A263" s="4">
         <v>376893</v>
       </c>
@@ -16484,8 +18093,14 @@
       <c r="Q263" s="7" t="s">
         <v>758</v>
       </c>
-    </row>
-    <row r="264" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R263" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S263" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="264" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A264" s="4">
         <v>376951</v>
       </c>
@@ -16535,8 +18150,14 @@
       <c r="Q264" s="7" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="265" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R264" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S264" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="265" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A265" s="4">
         <v>376992</v>
       </c>
@@ -16586,8 +18207,14 @@
       <c r="Q265" s="7" t="s">
         <v>760</v>
       </c>
-    </row>
-    <row r="266" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R265" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S265" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="266" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A266" s="4">
         <v>376896</v>
       </c>
@@ -16637,8 +18264,14 @@
       <c r="Q266" s="7" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="267" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R266" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S266" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="267" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A267" s="4">
         <v>376938</v>
       </c>
@@ -16688,8 +18321,14 @@
       <c r="Q267" s="7" t="s">
         <v>762</v>
       </c>
-    </row>
-    <row r="268" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R267" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S267" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="268" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A268" s="4">
         <v>376969</v>
       </c>
@@ -16739,8 +18378,14 @@
       <c r="Q268" s="7" t="s">
         <v>763</v>
       </c>
-    </row>
-    <row r="269" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R268" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S268" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="269" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A269" s="4">
         <v>376955</v>
       </c>
@@ -16790,8 +18435,14 @@
       <c r="Q269" s="7" t="s">
         <v>764</v>
       </c>
-    </row>
-    <row r="270" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R269" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S269" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="270" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A270" s="4">
         <v>376890</v>
       </c>
@@ -16841,8 +18492,14 @@
       <c r="Q270" s="7" t="s">
         <v>765</v>
       </c>
-    </row>
-    <row r="271" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R270" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S270" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="271" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A271" s="4">
         <v>376752</v>
       </c>
@@ -16892,8 +18549,14 @@
       <c r="Q271" s="7" t="s">
         <v>766</v>
       </c>
-    </row>
-    <row r="272" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R271" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S271" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="272" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A272" s="4">
         <v>376918</v>
       </c>
@@ -16943,8 +18606,14 @@
       <c r="Q272" s="7" t="s">
         <v>767</v>
       </c>
-    </row>
-    <row r="273" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R272" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S272" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="273" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A273" s="4">
         <v>376888</v>
       </c>
@@ -16994,8 +18663,14 @@
       <c r="Q273" s="7" t="s">
         <v>768</v>
       </c>
-    </row>
-    <row r="274" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R273" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S273" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="274" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A274" s="4">
         <v>376942</v>
       </c>
@@ -17045,8 +18720,14 @@
       <c r="Q274" s="7" t="s">
         <v>769</v>
       </c>
-    </row>
-    <row r="275" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R274" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S274" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="275" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A275" s="4">
         <v>376774</v>
       </c>
@@ -17096,8 +18777,14 @@
       <c r="Q275" s="7" t="s">
         <v>770</v>
       </c>
-    </row>
-    <row r="276" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R275" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S275" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="276" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A276" s="4">
         <v>376930</v>
       </c>
@@ -17147,8 +18834,14 @@
       <c r="Q276" s="7" t="s">
         <v>771</v>
       </c>
-    </row>
-    <row r="277" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R276" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S276" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="277" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A277" s="4">
         <v>376956</v>
       </c>
@@ -17198,8 +18891,14 @@
       <c r="Q277" s="7" t="s">
         <v>772</v>
       </c>
-    </row>
-    <row r="278" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R277" s="19">
+        <v>6.27</v>
+      </c>
+      <c r="S277" s="19">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="278" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A278" s="4">
         <v>376970</v>
       </c>
@@ -17249,8 +18948,14 @@
       <c r="Q278" s="7" t="s">
         <v>773</v>
       </c>
-    </row>
-    <row r="279" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R278" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S278" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="279" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A279" s="4">
         <v>376971</v>
       </c>
@@ -17300,8 +19005,14 @@
       <c r="Q279" s="7" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="280" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R279" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S279" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="280" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A280" s="4">
         <v>376754</v>
       </c>
@@ -17351,8 +19062,14 @@
       <c r="Q280" s="7" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="281" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R280" s="19">
+        <v>7.76</v>
+      </c>
+      <c r="S280" s="19">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="281" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A281" s="4">
         <v>376769</v>
       </c>
@@ -17402,8 +19119,14 @@
       <c r="Q281" s="7" t="s">
         <v>776</v>
       </c>
-    </row>
-    <row r="282" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R281" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S281" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="282" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A282" s="4">
         <v>377074</v>
       </c>
@@ -17453,8 +19176,14 @@
       <c r="Q282" s="7" t="s">
         <v>777</v>
       </c>
-    </row>
-    <row r="283" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R282" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S282" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="283" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A283" s="4">
         <v>376993</v>
       </c>
@@ -17504,8 +19233,14 @@
       <c r="Q283" s="7" t="s">
         <v>778</v>
       </c>
-    </row>
-    <row r="284" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R283" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S283" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="284" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A284" s="4">
         <v>376921</v>
       </c>
@@ -17555,8 +19290,14 @@
       <c r="Q284" s="7" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="285" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R284" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S284" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="285" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A285" s="4">
         <v>376920</v>
       </c>
@@ -17606,8 +19347,14 @@
       <c r="Q285" s="7" t="s">
         <v>780</v>
       </c>
-    </row>
-    <row r="286" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R285" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S285" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="286" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A286" s="4">
         <v>376925</v>
       </c>
@@ -17657,8 +19404,14 @@
       <c r="Q286" s="7" t="s">
         <v>781</v>
       </c>
-    </row>
-    <row r="287" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R286" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S286" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="287" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A287" s="4">
         <v>376933</v>
       </c>
@@ -17708,8 +19461,14 @@
       <c r="Q287" s="7" t="s">
         <v>782</v>
       </c>
-    </row>
-    <row r="288" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R287" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S287" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="288" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A288" s="4">
         <v>376929</v>
       </c>
@@ -17759,8 +19518,14 @@
       <c r="Q288" s="7" t="s">
         <v>783</v>
       </c>
-    </row>
-    <row r="289" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R288" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S288" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="289" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A289" s="4">
         <v>376765</v>
       </c>
@@ -17810,8 +19575,14 @@
       <c r="Q289" s="7" t="s">
         <v>784</v>
       </c>
-    </row>
-    <row r="290" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R289" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S289" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="290" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A290" s="4">
         <v>376957</v>
       </c>
@@ -17861,8 +19632,14 @@
       <c r="Q290" s="7" t="s">
         <v>785</v>
       </c>
-    </row>
-    <row r="291" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R290" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S290" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="291" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A291" s="4">
         <v>376873</v>
       </c>
@@ -17912,8 +19689,14 @@
       <c r="Q291" s="7" t="s">
         <v>786</v>
       </c>
-    </row>
-    <row r="292" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R291" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S291" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="292" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A292" s="4">
         <v>376950</v>
       </c>
@@ -17963,8 +19746,14 @@
       <c r="Q292" s="7" t="s">
         <v>787</v>
       </c>
-    </row>
-    <row r="293" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R292" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S292" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="293" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A293" s="4">
         <v>376886</v>
       </c>
@@ -18014,8 +19803,14 @@
       <c r="Q293" s="7" t="s">
         <v>788</v>
       </c>
-    </row>
-    <row r="294" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R293" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S293" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="294" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A294" s="4">
         <v>376936</v>
       </c>
@@ -18065,8 +19860,14 @@
       <c r="Q294" s="7" t="s">
         <v>789</v>
       </c>
-    </row>
-    <row r="295" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R294" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S294" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="295" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A295" s="4">
         <v>376961</v>
       </c>
@@ -18116,8 +19917,14 @@
       <c r="Q295" s="7" t="s">
         <v>790</v>
       </c>
-    </row>
-    <row r="296" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R295" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S295" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="296" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A296" s="4">
         <v>377076</v>
       </c>
@@ -18167,8 +19974,14 @@
       <c r="Q296" s="7" t="s">
         <v>791</v>
       </c>
-    </row>
-    <row r="297" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R296" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S296" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="297" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A297" s="4">
         <v>376922</v>
       </c>
@@ -18218,8 +20031,14 @@
       <c r="Q297" s="7" t="s">
         <v>792</v>
       </c>
-    </row>
-    <row r="298" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R297" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S297" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="298" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A298" s="4">
         <v>376764</v>
       </c>
@@ -18269,8 +20088,14 @@
       <c r="Q298" s="7" t="s">
         <v>793</v>
       </c>
-    </row>
-    <row r="299" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R298" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S298" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="299" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A299" s="4">
         <v>376972</v>
       </c>
@@ -18320,8 +20145,14 @@
       <c r="Q299" s="7" t="s">
         <v>794</v>
       </c>
-    </row>
-    <row r="300" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R299" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S299" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="300" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A300" s="4">
         <v>376875</v>
       </c>
@@ -18371,8 +20202,14 @@
       <c r="Q300" s="7" t="s">
         <v>795</v>
       </c>
-    </row>
-    <row r="301" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R300" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S300" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="301" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A301" s="4">
         <v>376927</v>
       </c>
@@ -18422,8 +20259,14 @@
       <c r="Q301" s="7" t="s">
         <v>796</v>
       </c>
-    </row>
-    <row r="302" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R301" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S301" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="302" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A302" s="4">
         <v>376870</v>
       </c>
@@ -18473,8 +20316,14 @@
       <c r="Q302" s="7" t="s">
         <v>797</v>
       </c>
-    </row>
-    <row r="303" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R302" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S302" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="303" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A303" s="4">
         <v>376939</v>
       </c>
@@ -18524,8 +20373,14 @@
       <c r="Q303" s="7" t="s">
         <v>798</v>
       </c>
-    </row>
-    <row r="304" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R303" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S303" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="304" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A304" s="4">
         <v>376771</v>
       </c>
@@ -18575,8 +20430,14 @@
       <c r="Q304" s="7" t="s">
         <v>799</v>
       </c>
-    </row>
-    <row r="305" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R304" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S304" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="305" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A305" s="4">
         <v>376934</v>
       </c>
@@ -18626,8 +20487,14 @@
       <c r="Q305" s="7" t="s">
         <v>800</v>
       </c>
-    </row>
-    <row r="306" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R305" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S305" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="306" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A306" s="4">
         <v>376869</v>
       </c>
@@ -18677,8 +20544,14 @@
       <c r="Q306" s="7" t="s">
         <v>801</v>
       </c>
-    </row>
-    <row r="307" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R306" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S306" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="307" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A307" s="4">
         <v>376940</v>
       </c>
@@ -18728,8 +20601,14 @@
       <c r="Q307" s="7" t="s">
         <v>802</v>
       </c>
-    </row>
-    <row r="308" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R307" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S307" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="308" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A308" s="4">
         <v>376773</v>
       </c>
@@ -18779,8 +20658,14 @@
       <c r="Q308" s="7" t="s">
         <v>803</v>
       </c>
-    </row>
-    <row r="309" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R308" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S308" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="309" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A309" s="4">
         <v>376884</v>
       </c>
@@ -18830,8 +20715,14 @@
       <c r="Q309" s="7" t="s">
         <v>804</v>
       </c>
-    </row>
-    <row r="310" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R309" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S309" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="310" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A310" s="4">
         <v>376949</v>
       </c>
@@ -18881,8 +20772,14 @@
       <c r="Q310" s="7" t="e">
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="311" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R310" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S310" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="311" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A311" s="4">
         <v>376935</v>
       </c>
@@ -18932,8 +20829,14 @@
       <c r="Q311" s="7" t="s">
         <v>805</v>
       </c>
-    </row>
-    <row r="312" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R311" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S311" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="312" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A312" s="4">
         <v>376968</v>
       </c>
@@ -18983,8 +20886,14 @@
       <c r="Q312" s="7" t="s">
         <v>806</v>
       </c>
-    </row>
-    <row r="313" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R312" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S312" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="313" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A313" s="4">
         <v>376967</v>
       </c>
@@ -19034,8 +20943,14 @@
       <c r="Q313" s="7" t="s">
         <v>807</v>
       </c>
-    </row>
-    <row r="314" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R313" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S313" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="314" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A314" s="4">
         <v>376770</v>
       </c>
@@ -19085,8 +21000,14 @@
       <c r="Q314" s="7" t="s">
         <v>808</v>
       </c>
-    </row>
-    <row r="315" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R314" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S314" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="315" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A315" s="4">
         <v>376924</v>
       </c>
@@ -19136,8 +21057,14 @@
       <c r="Q315" s="7" t="s">
         <v>809</v>
       </c>
-    </row>
-    <row r="316" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R315" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S315" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="316" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A316" s="4">
         <v>376755</v>
       </c>
@@ -19187,8 +21114,14 @@
       <c r="Q316" s="7" t="s">
         <v>810</v>
       </c>
-    </row>
-    <row r="317" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R316" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S316" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="317" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A317" s="4">
         <v>376864</v>
       </c>
@@ -19238,8 +21171,14 @@
       <c r="Q317" s="7" t="s">
         <v>811</v>
       </c>
-    </row>
-    <row r="318" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R317" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S317" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="318" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A318" s="4">
         <v>376868</v>
       </c>
@@ -19289,8 +21228,14 @@
       <c r="Q318" s="7" t="s">
         <v>812</v>
       </c>
-    </row>
-    <row r="319" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R318" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S318" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="319" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A319" s="4">
         <v>376889</v>
       </c>
@@ -19340,8 +21285,14 @@
       <c r="Q319" s="7" t="s">
         <v>813</v>
       </c>
-    </row>
-    <row r="320" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R319" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S319" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="320" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A320" s="4">
         <v>376931</v>
       </c>
@@ -19391,8 +21342,14 @@
       <c r="Q320" s="7" t="s">
         <v>814</v>
       </c>
-    </row>
-    <row r="321" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R320" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S320" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="321" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A321" s="4">
         <v>376876</v>
       </c>
@@ -19442,8 +21399,14 @@
       <c r="Q321" s="7" t="s">
         <v>815</v>
       </c>
-    </row>
-    <row r="322" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R321" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S321" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="322" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A322" s="4">
         <v>376994</v>
       </c>
@@ -19493,8 +21456,14 @@
       <c r="Q322" s="7" t="s">
         <v>816</v>
       </c>
-    </row>
-    <row r="323" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R322" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S322" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="323" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A323" s="4">
         <v>376832</v>
       </c>
@@ -19544,8 +21513,14 @@
       <c r="Q323" s="7" t="s">
         <v>817</v>
       </c>
-    </row>
-    <row r="324" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R323" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S323" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="324" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A324" s="4">
         <v>376941</v>
       </c>
@@ -19595,8 +21570,14 @@
       <c r="Q324" s="7" t="s">
         <v>818</v>
       </c>
-    </row>
-    <row r="325" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R324" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S324" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="325" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A325" s="4">
         <v>376887</v>
       </c>
@@ -19646,8 +21627,14 @@
       <c r="Q325" s="7" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="326" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R325" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S325" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="326" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A326" s="4">
         <v>376947</v>
       </c>
@@ -19697,8 +21684,14 @@
       <c r="Q326" s="7" t="s">
         <v>820</v>
       </c>
-    </row>
-    <row r="327" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R326" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S326" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="327" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A327" s="4">
         <v>376883</v>
       </c>
@@ -19748,8 +21741,14 @@
       <c r="Q327" s="7" t="s">
         <v>821</v>
       </c>
-    </row>
-    <row r="328" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R327" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S327" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="328" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A328" s="4">
         <v>376865</v>
       </c>
@@ -19799,8 +21798,14 @@
       <c r="Q328" s="7" t="s">
         <v>822</v>
       </c>
-    </row>
-    <row r="329" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R328" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S328" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="329" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A329" s="4">
         <v>376919</v>
       </c>
@@ -19850,8 +21855,14 @@
       <c r="Q329" s="7" t="s">
         <v>823</v>
       </c>
-    </row>
-    <row r="330" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R329" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S329" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="330" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A330" s="4">
         <v>376340</v>
       </c>
@@ -19901,8 +21912,14 @@
       <c r="Q330" s="7" t="s">
         <v>824</v>
       </c>
-    </row>
-    <row r="331" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R330" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S330" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="331" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A331" s="4">
         <v>376338</v>
       </c>
@@ -19952,8 +21969,14 @@
       <c r="Q331" s="7" t="s">
         <v>825</v>
       </c>
-    </row>
-    <row r="332" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R331" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S331" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="332" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A332" s="4">
         <v>376966</v>
       </c>
@@ -20003,8 +22026,14 @@
       <c r="Q332" s="7" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="333" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R332" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S332" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="333" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A333" s="4">
         <v>377071</v>
       </c>
@@ -20054,8 +22083,14 @@
       <c r="Q333" s="7" t="s">
         <v>827</v>
       </c>
-    </row>
-    <row r="334" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R333" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S333" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="334" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A334" s="4">
         <v>371480</v>
       </c>
@@ -20105,8 +22140,14 @@
       <c r="Q334" s="7" t="s">
         <v>828</v>
       </c>
-    </row>
-    <row r="335" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R334" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S334" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="335" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A335" s="4">
         <v>376965</v>
       </c>
@@ -20156,8 +22197,14 @@
       <c r="Q335" s="7" t="s">
         <v>829</v>
       </c>
-    </row>
-    <row r="336" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R335" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S335" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="336" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A336" s="4">
         <v>371482</v>
       </c>
@@ -20207,8 +22254,14 @@
       <c r="Q336" s="7" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="337" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R336" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S336" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="337" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A337" s="4">
         <v>371484</v>
       </c>
@@ -20258,8 +22311,14 @@
       <c r="Q337" s="7" t="s">
         <v>831</v>
       </c>
-    </row>
-    <row r="338" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R337" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S337" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="338" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A338" s="4">
         <v>371485</v>
       </c>
@@ -20309,8 +22368,14 @@
       <c r="Q338" s="7" t="s">
         <v>832</v>
       </c>
-    </row>
-    <row r="339" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R338" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S338" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="339" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A339" s="4">
         <v>376830</v>
       </c>
@@ -20360,8 +22425,14 @@
       <c r="Q339" s="7" t="s">
         <v>833</v>
       </c>
-    </row>
-    <row r="340" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R339" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S339" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="340" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A340" s="4">
         <v>371486</v>
       </c>
@@ -20411,8 +22482,14 @@
       <c r="Q340" s="7" t="s">
         <v>834</v>
       </c>
-    </row>
-    <row r="341" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R340" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S340" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="341" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A341" s="4">
         <v>377073</v>
       </c>
@@ -20462,8 +22539,14 @@
       <c r="Q341" s="7" t="s">
         <v>835</v>
       </c>
-    </row>
-    <row r="342" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R341" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S341" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="342" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A342" s="4">
         <v>371488</v>
       </c>
@@ -20513,8 +22596,14 @@
       <c r="Q342" s="7" t="s">
         <v>836</v>
       </c>
-    </row>
-    <row r="343" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R342" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S342" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="343" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A343" s="4">
         <v>371489</v>
       </c>
@@ -20564,8 +22653,14 @@
       <c r="Q343" s="7" t="s">
         <v>837</v>
       </c>
-    </row>
-    <row r="344" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R343" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S343" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="344" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A344" s="4">
         <v>371490</v>
       </c>
@@ -20615,8 +22710,14 @@
       <c r="Q344" s="7" t="s">
         <v>838</v>
       </c>
-    </row>
-    <row r="345" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R344" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S344" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="345" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A345" s="4">
         <v>371492</v>
       </c>
@@ -20666,8 +22767,14 @@
       <c r="Q345" s="7" t="s">
         <v>839</v>
       </c>
-    </row>
-    <row r="346" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R345" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S345" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="346" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A346" s="4">
         <v>376963</v>
       </c>
@@ -20717,8 +22824,14 @@
       <c r="Q346" s="7" t="s">
         <v>840</v>
       </c>
-    </row>
-    <row r="347" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R346" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S346" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="347" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A347" s="4">
         <v>376779</v>
       </c>
@@ -20768,8 +22881,14 @@
       <c r="Q347" s="7" t="s">
         <v>841</v>
       </c>
-    </row>
-    <row r="348" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R347" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S347" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="348" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A348" s="4">
         <v>376778</v>
       </c>
@@ -20819,8 +22938,14 @@
       <c r="Q348" s="7" t="s">
         <v>842</v>
       </c>
-    </row>
-    <row r="349" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R348" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S348" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="349" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A349" s="4">
         <v>371497</v>
       </c>
@@ -20870,10 +22995,16 @@
       <c r="Q349" s="7" t="s">
         <v>843</v>
       </c>
+      <c r="R349" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="S349" s="19" t="s">
+        <v>190</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B349">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -20883,6 +23014,1522 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C466E9D-A88C-42A8-A83F-60980D5C74C8}">
+  <dimension ref="A1:S26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="44.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="74.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.42578125" style="17" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.85546875" style="17" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="R1" s="15" t="s">
+        <v>844</v>
+      </c>
+      <c r="S1" s="15" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>376560</v>
+      </c>
+      <c r="B2" s="5">
+        <v>4867340</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="6">
+        <v>46139</v>
+      </c>
+      <c r="E2" s="6"/>
+      <c r="F2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="6">
+        <v>35401</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="5">
+        <v>38575133810</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="R2" s="16">
+        <v>2.99</v>
+      </c>
+      <c r="S2" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>376297</v>
+      </c>
+      <c r="B3" s="5">
+        <v>4867256</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="6">
+        <v>46139</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="6">
+        <v>30950</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="5">
+        <v>34056806896</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="R3" s="16">
+        <v>6.83</v>
+      </c>
+      <c r="S3" s="16">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>376299</v>
+      </c>
+      <c r="B4" s="5">
+        <v>4867258</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="6">
+        <v>46139</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="6">
+        <v>34255</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="5">
+        <v>41300775890</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="Q4" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="R4" s="16">
+        <v>2.42</v>
+      </c>
+      <c r="S4" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>376300</v>
+      </c>
+      <c r="B5" s="5">
+        <v>4867259</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="6">
+        <v>46139</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="6">
+        <v>35935</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="5">
+        <v>48531233852</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="R5" s="16">
+        <v>10.65</v>
+      </c>
+      <c r="S5" s="16">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>376304</v>
+      </c>
+      <c r="B6" s="5">
+        <v>4867262</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="6">
+        <v>46139</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="6">
+        <v>37307</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="5">
+        <v>56007656810</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="Q6" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="R6" s="16">
+        <v>9.2100000000000009</v>
+      </c>
+      <c r="S6" s="16">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>376314</v>
+      </c>
+      <c r="B7" s="5">
+        <v>4867272</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" s="6">
+        <v>46139</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="6">
+        <v>36850</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="5">
+        <v>48356919894</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q7" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="R7" s="16">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="S7" s="16">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>376367</v>
+      </c>
+      <c r="B8" s="5">
+        <v>4867298</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" s="6">
+        <v>46139</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="6">
+        <v>35872</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="5">
+        <v>2408464277</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="R8" s="16">
+        <v>6.79</v>
+      </c>
+      <c r="S8" s="16">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>376398</v>
+      </c>
+      <c r="B9" s="5">
+        <v>4867325</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D9" s="6">
+        <v>46139</v>
+      </c>
+      <c r="E9" s="6"/>
+      <c r="F9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="6">
+        <v>33780</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="5">
+        <v>39903755805</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q9" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="R9" s="16">
+        <v>13.34</v>
+      </c>
+      <c r="S9" s="16">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>376372</v>
+      </c>
+      <c r="B10" s="5">
+        <v>4867303</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D10" s="6">
+        <v>46139</v>
+      </c>
+      <c r="E10" s="6"/>
+      <c r="F10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="6">
+        <v>27883</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="5">
+        <v>26363677807</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="Q10" s="7" t="s">
+        <v>605</v>
+      </c>
+      <c r="R10" s="16">
+        <v>2.7</v>
+      </c>
+      <c r="S10" s="16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>376361</v>
+      </c>
+      <c r="B11" s="5">
+        <v>4867296</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D11" s="6">
+        <v>46139</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="F11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="6">
+        <v>32619</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="5">
+        <v>37758809847</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>611</v>
+      </c>
+      <c r="R11" s="16">
+        <v>10.1</v>
+      </c>
+      <c r="S11" s="16">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>376374</v>
+      </c>
+      <c r="B12" s="5">
+        <v>4867305</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D12" s="6">
+        <v>46139</v>
+      </c>
+      <c r="E12" s="6"/>
+      <c r="F12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="6">
+        <v>39255</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="5">
+        <v>45998589866</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="P12" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="Q12" s="7" t="s">
+        <v>614</v>
+      </c>
+      <c r="R12" s="16">
+        <v>4.58</v>
+      </c>
+      <c r="S12" s="16">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>376376</v>
+      </c>
+      <c r="B13" s="5">
+        <v>4867307</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D13" s="6">
+        <v>46139</v>
+      </c>
+      <c r="E13" s="6"/>
+      <c r="F13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="6">
+        <v>35697</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="5">
+        <v>48018578842</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="P13" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q13" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="R13" s="16">
+        <v>18.68</v>
+      </c>
+      <c r="S13" s="16">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>376377</v>
+      </c>
+      <c r="B14" s="5">
+        <v>4867308</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D14" s="6">
+        <v>46139</v>
+      </c>
+      <c r="E14" s="6"/>
+      <c r="F14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="6">
+        <v>33499</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="5">
+        <v>60289765390</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="P14" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q14" s="7" t="s">
+        <v>646</v>
+      </c>
+      <c r="R14" s="16">
+        <v>3.6</v>
+      </c>
+      <c r="S14" s="16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>376397</v>
+      </c>
+      <c r="B15" s="5">
+        <v>4774710</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D15" s="6">
+        <v>46139</v>
+      </c>
+      <c r="E15" s="6"/>
+      <c r="F15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="6">
+        <v>30987</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="5">
+        <v>33442891876</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>657</v>
+      </c>
+      <c r="R15" s="16">
+        <v>24</v>
+      </c>
+      <c r="S15" s="16">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>376384</v>
+      </c>
+      <c r="B16" s="5">
+        <v>4867315</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D16" s="6">
+        <v>46139</v>
+      </c>
+      <c r="E16" s="6"/>
+      <c r="F16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="6">
+        <v>29249</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="5">
+        <v>32163032841</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="O16" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="P16" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="R16" s="16">
+        <v>2.87</v>
+      </c>
+      <c r="S16" s="16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>370793</v>
+      </c>
+      <c r="B17" s="5">
+        <v>4860713</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D17" s="6">
+        <v>46129</v>
+      </c>
+      <c r="E17" s="6"/>
+      <c r="F17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="I17" s="5">
+        <v>14232361812</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q17" s="7" t="s">
+        <v>676</v>
+      </c>
+      <c r="R17" s="16">
+        <v>1.91</v>
+      </c>
+      <c r="S17" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>370675</v>
+      </c>
+      <c r="B18" s="5">
+        <v>4860596</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D18" s="6">
+        <v>46129</v>
+      </c>
+      <c r="E18" s="6"/>
+      <c r="F18" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="I18" s="5">
+        <v>48775429810</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="O18" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="P18" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="Q18" s="7" t="s">
+        <v>692</v>
+      </c>
+      <c r="R18" s="16">
+        <v>33.93</v>
+      </c>
+      <c r="S18" s="16">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>370292</v>
+      </c>
+      <c r="B19" s="5">
+        <v>4861301</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="D19" s="6">
+        <v>46129</v>
+      </c>
+      <c r="E19" s="6"/>
+      <c r="F19" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="I19" s="5">
+        <v>49017492856</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="P19" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="Q19" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="R19" s="16">
+        <v>38.450000000000003</v>
+      </c>
+      <c r="S19" s="16">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>370738</v>
+      </c>
+      <c r="B20" s="5">
+        <v>4860658</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="D20" s="6">
+        <v>46129</v>
+      </c>
+      <c r="E20" s="6"/>
+      <c r="F20" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="I20" s="5">
+        <v>54162927847</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="O20" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="P20" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="Q20" s="7" t="s">
+        <v>694</v>
+      </c>
+      <c r="R20" s="16">
+        <v>33.17</v>
+      </c>
+      <c r="S20" s="16">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>376874</v>
+      </c>
+      <c r="B21" s="5">
+        <v>4867681</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="D21" s="6">
+        <v>46146</v>
+      </c>
+      <c r="E21" s="6"/>
+      <c r="F21" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="6">
+        <v>36622</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="5">
+        <v>50130036870</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="P21" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="Q21" s="7" t="s">
+        <v>725</v>
+      </c>
+      <c r="R21" s="16">
+        <v>1.43</v>
+      </c>
+      <c r="S21" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <v>376780</v>
+      </c>
+      <c r="B22" s="5">
+        <v>4867667</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="D22" s="6">
+        <v>46146</v>
+      </c>
+      <c r="E22" s="6"/>
+      <c r="F22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="6">
+        <v>31674</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="5">
+        <v>35331791840</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="O22" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="P22" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q22" s="7" t="s">
+        <v>726</v>
+      </c>
+      <c r="R22" s="16">
+        <v>13.51</v>
+      </c>
+      <c r="S22" s="16">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
+        <v>376772</v>
+      </c>
+      <c r="B23" s="5">
+        <v>4867660</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D23" s="6">
+        <v>46146</v>
+      </c>
+      <c r="E23" s="6"/>
+      <c r="F23" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="6">
+        <v>38682</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="5">
+        <v>54358820875</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="P23" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="Q23" s="7" t="s">
+        <v>737</v>
+      </c>
+      <c r="R23" s="16">
+        <v>1.73</v>
+      </c>
+      <c r="S23" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
+        <v>376953</v>
+      </c>
+      <c r="B24" s="5">
+        <v>4867732</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="D24" s="6">
+        <v>46146</v>
+      </c>
+      <c r="E24" s="6"/>
+      <c r="F24" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="6">
+        <v>31860</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="5">
+        <v>36145171871</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="O24" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="P24" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q24" s="7" t="s">
+        <v>753</v>
+      </c>
+      <c r="R24" s="16">
+        <v>23.97</v>
+      </c>
+      <c r="S24" s="16">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <v>376956</v>
+      </c>
+      <c r="B25" s="5">
+        <v>4867735</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D25" s="6">
+        <v>46146</v>
+      </c>
+      <c r="E25" s="6"/>
+      <c r="F25" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="6">
+        <v>39510</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="5">
+        <v>50193763885</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q25" s="7" t="s">
+        <v>772</v>
+      </c>
+      <c r="R25" s="16">
+        <v>6.27</v>
+      </c>
+      <c r="S25" s="16">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <v>376754</v>
+      </c>
+      <c r="B26" s="5">
+        <v>4867641</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="D26" s="6">
+        <v>46146</v>
+      </c>
+      <c r="E26" s="6"/>
+      <c r="F26" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" s="6">
+        <v>35912</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26" s="5">
+        <v>49511480804</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="N26" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="O26" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="P26" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q26" s="7" t="s">
+        <v>775</v>
+      </c>
+      <c r="R26" s="16">
+        <v>7.76</v>
+      </c>
+      <c r="S26" s="16">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B2:B26">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71A979CD-565D-480D-90A1-D33351D19641}">
   <dimension ref="B10:D19"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -20912,7 +24559,7 @@
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="14">
-        <f>COUNTIFS(Nominal!K:K,Resumo!B11)</f>
+        <f>COUNTIFS('Nominal Geral'!K:K,Resumo!B11)</f>
         <v>5</v>
       </c>
     </row>
@@ -20922,7 +24569,7 @@
       </c>
       <c r="C12" s="12"/>
       <c r="D12" s="14">
-        <f>COUNTIFS(Nominal!K:K,Resumo!B12)</f>
+        <f>COUNTIFS('Nominal Geral'!K:K,Resumo!B12)</f>
         <v>4</v>
       </c>
     </row>
@@ -20932,7 +24579,7 @@
       </c>
       <c r="C13" s="12"/>
       <c r="D13" s="14">
-        <f>COUNTIFS(Nominal!K:K,Resumo!B13)</f>
+        <f>COUNTIFS('Nominal Geral'!K:K,Resumo!B13)</f>
         <v>303</v>
       </c>
     </row>
@@ -20942,7 +24589,7 @@
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="14">
-        <f>COUNTIFS(Nominal!K:K,Resumo!B14)</f>
+        <f>COUNTIFS('Nominal Geral'!K:K,Resumo!B14)</f>
         <v>4</v>
       </c>
     </row>
@@ -20952,7 +24599,7 @@
       </c>
       <c r="C15" s="12"/>
       <c r="D15" s="14">
-        <f>COUNTIFS(Nominal!K:K,Resumo!B15)</f>
+        <f>COUNTIFS('Nominal Geral'!K:K,Resumo!B15)</f>
         <v>1</v>
       </c>
     </row>
@@ -20962,7 +24609,7 @@
       </c>
       <c r="C16" s="12"/>
       <c r="D16" s="14">
-        <f>COUNTIFS(Nominal!K:K,Resumo!B16)</f>
+        <f>COUNTIFS('Nominal Geral'!K:K,Resumo!B16)</f>
         <v>1</v>
       </c>
     </row>
@@ -20972,7 +24619,7 @@
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="14">
-        <f>COUNTIFS(Nominal!K:K,Resumo!B17)</f>
+        <f>COUNTIFS('Nominal Geral'!K:K,Resumo!B17)</f>
         <v>16</v>
       </c>
     </row>
@@ -20982,7 +24629,7 @@
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="14">
-        <f>COUNTIFS(Nominal!K:K,Resumo!B18)</f>
+        <f>COUNTIFS('Nominal Geral'!K:K,Resumo!B18)</f>
         <v>14</v>
       </c>
     </row>
